--- a/artfynd/A 2055-2025 artfynd.xlsx
+++ b/artfynd/A 2055-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>123700730</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,6 +784,1039 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123712996</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sågen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>514809</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6731156</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Två bilder på en av körvägarna i den ännu bara avverkningsanmälda skogen. Bilderna visar båda riktningar. Med vit sten, 74° ÖNÖ, N 514796, Ö 9731169 (10)  Lerig väg, 269° W, N 514794 Ö 6731162 (11)</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123713005</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>sågen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>514848</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6731141</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>En planta är uppdragen men det har inte jag gjord. Uppskattat antal, det kan vara flera.  (98)</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123713001</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>sågen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>514842</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6731143</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>(03)</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123712972</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sågen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>514858</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6731044</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En bild på Knärot från en giltig avverkningsanmälan mellan en ännu ej giltig anmälan och en avverkad anmälan. I alla tre, samt i ett område som Mellanskog har gallrat) finns Knärot. Inget område hade någon Hänsynsmarkering för Knärot. Uppskattat antal. En miljöbild tagen i samma anmälan (76, 77)</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123713000</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sågen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>514819</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6731154</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>(05)</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123749142</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5174</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SÅGEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>514789</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6731161</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>på gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123712997</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>sågen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>514808</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6731147</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I angränsande avverkningsanmälan. I ravinen ner mot det troligen utdikade området. Uppskattat antal.  (08)</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123712998</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>sågen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>514817</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6731152</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>(06) (07)</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2055-2025 artfynd.xlsx
+++ b/artfynd/A 2055-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123700730</v>
+        <v>123712972</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sågen, Sågen, Dlr</t>
+          <t>Sågen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514792</v>
+        <v>514858</v>
       </c>
       <c r="R2" t="n">
-        <v>6731163</v>
+        <v>6731044</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>En bild på Knärot från en giltig avverkningsanmälan mellan en ännu ej giltig anmälan och en avverkad anmälan. I alla tre, samt i ett område som Mellanskog har gallrat) finns Knärot. Inget område hade någon Hänsynsmarkering för Knärot. Uppskattat antal. En miljöbild tagen i samma anmälan (76, 77)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +786,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123712996</v>
+        <v>123713005</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,14 +853,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sågen, Dlr</t>
+          <t>sågen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514809</v>
+        <v>514848</v>
       </c>
       <c r="R3" t="n">
-        <v>6731156</v>
+        <v>6731141</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,12 +902,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Två bilder på en av körvägarna i den ännu bara avverkningsanmälda skogen. Bilderna visar båda riktningar. Med vit sten, 74° ÖNÖ, N 514796, Ö 9731169 (10)  Lerig väg, 269° W, N 514794 Ö 6731162 (11)</t>
+          <t>En planta är uppdragen men det har inte jag gjord. Uppskattat antal, det kan vara flera.  (98)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123713005</v>
+        <v>123713001</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,7 +970,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -969,10 +987,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514848</v>
+        <v>514842</v>
       </c>
       <c r="R4" t="n">
-        <v>6731141</v>
+        <v>6731143</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1004,7 +1022,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,12 +1032,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En planta är uppdragen men det har inte jag gjord. Uppskattat antal, det kan vara flera.  (98)</t>
+          <t>(03)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123713001</v>
+        <v>123712998</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,7 +1100,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1099,10 +1117,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514842</v>
+        <v>514817</v>
       </c>
       <c r="R5" t="n">
-        <v>6731143</v>
+        <v>6731152</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1134,7 +1152,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,12 +1162,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>(03)</t>
+          <t>(06) (07)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123712972</v>
+        <v>123712997</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1212,7 +1230,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1225,14 +1243,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sågen, Dlr</t>
+          <t>sågen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514858</v>
+        <v>514808</v>
       </c>
       <c r="R6" t="n">
-        <v>6731044</v>
+        <v>6731147</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1264,7 +1282,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1274,12 +1292,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>En bild på Knärot från en giltig avverkningsanmälan mellan en ännu ej giltig anmälan och en avverkad anmälan. I alla tre, samt i ett område som Mellanskog har gallrat) finns Knärot. Inget område hade någon Hänsynsmarkering för Knärot. Uppskattat antal. En miljöbild tagen i samma anmälan (76, 77)</t>
+          <t>I angränsande avverkningsanmälan. I ravinen ner mot det troligen utdikade området. Uppskattat antal.  (08)</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1310,7 +1328,7 @@
         <v>123713000</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1440,7 +1458,7 @@
         <v>123749142</v>
       </c>
       <c r="B8" t="n">
-        <v>5174</v>
+        <v>5176</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1560,10 +1578,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123712997</v>
+        <v>123712996</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1608,14 +1626,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>sågen, Dlr</t>
+          <t>Sågen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514808</v>
+        <v>514809</v>
       </c>
       <c r="R9" t="n">
-        <v>6731147</v>
+        <v>6731156</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1647,7 +1665,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1657,12 +1675,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I angränsande avverkningsanmälan. I ravinen ner mot det troligen utdikade området. Uppskattat antal.  (08)</t>
+          <t>Två bilder på en av körvägarna i den ännu bara avverkningsanmälda skogen. Bilderna visar båda riktningar. Med vit sten, 74° ÖNÖ, N 514796, Ö 9731169 (10)  Lerig väg, 269° W, N 514794 Ö 6731162 (11)</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1687,136 +1705,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>123712998</v>
-      </c>
-      <c r="B10" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>sågen, Dlr</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>514817</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6731152</v>
-      </c>
-      <c r="S10" t="n">
-        <v>15</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Bjursås</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>19:08</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>19:08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>(06) (07)</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2055-2025 artfynd.xlsx
+++ b/artfynd/A 2055-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123712972</v>
+        <v>123749142</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>5176</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sågen, Dlr</t>
+          <t>SÅGEN, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514858</v>
+        <v>514789</v>
       </c>
       <c r="R2" t="n">
-        <v>6731044</v>
+        <v>6731161</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>En bild på Knärot från en giltig avverkningsanmälan mellan en ännu ej giltig anmälan och en avverkad anmälan. I alla tre, samt i ett område som Mellanskog har gallrat) finns Knärot. Inget område hade någon Hänsynsmarkering för Knärot. Uppskattat antal. En miljöbild tagen i samma anmälan (76, 77)</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123713005</v>
+        <v>123712972</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -853,14 +846,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>sågen, Dlr</t>
+          <t>Sågen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514848</v>
+        <v>514858</v>
       </c>
       <c r="R3" t="n">
-        <v>6731141</v>
+        <v>6731044</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -892,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,12 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>En planta är uppdragen men det har inte jag gjord. Uppskattat antal, det kan vara flera.  (98)</t>
+          <t>En bild på Knärot från en giltig avverkningsanmälan mellan en ännu ej giltig anmälan och en avverkad anmälan. I alla tre, samt i ett område som Mellanskog har gallrat) finns Knärot. Inget område hade någon Hänsynsmarkering för Knärot. Uppskattat antal. En miljöbild tagen i samma anmälan (76, 77)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123713001</v>
+        <v>123712997</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,7 +963,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514842</v>
+        <v>514808</v>
       </c>
       <c r="R4" t="n">
-        <v>6731143</v>
+        <v>6731147</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1022,7 +1015,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,12 +1025,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>(03)</t>
+          <t>I angränsande avverkningsanmälan. I ravinen ner mot det troligen utdikade området. Uppskattat antal.  (08)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123712998</v>
+        <v>123713000</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1100,7 +1093,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1113,14 +1106,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>sågen, Dlr</t>
+          <t>Sågen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514817</v>
+        <v>514819</v>
       </c>
       <c r="R5" t="n">
-        <v>6731152</v>
+        <v>6731154</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1152,7 +1145,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1162,12 +1155,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>(06) (07)</t>
+          <t>(05)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1188,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123712997</v>
+        <v>123713001</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1230,7 +1223,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1247,10 +1240,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514808</v>
+        <v>514842</v>
       </c>
       <c r="R6" t="n">
-        <v>6731147</v>
+        <v>6731143</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1282,7 +1275,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1292,12 +1285,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I angränsande avverkningsanmälan. I ravinen ner mot det troligen utdikade området. Uppskattat antal.  (08)</t>
+          <t>(03)</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1325,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123713000</v>
+        <v>123712998</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1360,7 +1353,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1373,14 +1366,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sågen, Dlr</t>
+          <t>sågen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514819</v>
+        <v>514817</v>
       </c>
       <c r="R7" t="n">
-        <v>6731154</v>
+        <v>6731152</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1412,7 +1405,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1422,12 +1415,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>(05)</t>
+          <t>(06) (07)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,10 +1448,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123749142</v>
+        <v>123712996</v>
       </c>
       <c r="B8" t="n">
-        <v>5176</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1467,46 +1460,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SÅGEN, Dlr</t>
+          <t>Sågen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514789</v>
+        <v>514809</v>
       </c>
       <c r="R8" t="n">
-        <v>6731161</v>
+        <v>6731156</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>Två bilder på en av körvägarna i den ännu bara avverkningsanmälda skogen. Bilderna visar båda riktningar. Med vit sten, 74° ÖNÖ, N 514796, Ö 9731169 (10)  Lerig väg, 269° W, N 514794 Ö 6731162 (11)</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1578,10 +1578,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123712996</v>
+        <v>123713005</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1626,14 +1626,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sågen, Dlr</t>
+          <t>sågen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514809</v>
+        <v>514848</v>
       </c>
       <c r="R9" t="n">
-        <v>6731156</v>
+        <v>6731141</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Två bilder på en av körvägarna i den ännu bara avverkningsanmälda skogen. Bilderna visar båda riktningar. Med vit sten, 74° ÖNÖ, N 514796, Ö 9731169 (10)  Lerig väg, 269° W, N 514794 Ö 6731162 (11)</t>
+          <t>En planta är uppdragen men det har inte jag gjord. Uppskattat antal, det kan vara flera.  (98)</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 2055-2025 artfynd.xlsx
+++ b/artfynd/A 2055-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123713001</v>
+        <v>123712998</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514842</v>
+        <v>514817</v>
       </c>
       <c r="R2" t="n">
-        <v>6731143</v>
+        <v>6731152</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>(03)</t>
+          <t>(06) (07)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123712997</v>
+        <v>123712972</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,14 +853,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>sågen, Dlr</t>
+          <t>Sågen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514808</v>
+        <v>514858</v>
       </c>
       <c r="R3" t="n">
-        <v>6731147</v>
+        <v>6731044</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I angränsande avverkningsanmälan. I ravinen ner mot det troligen utdikade området. Uppskattat antal.  (08)</t>
+          <t>En bild på Knärot från en giltig avverkningsanmälan mellan en ännu ej giltig anmälan och en avverkad anmälan. I alla tre, samt i ett område som Mellanskog har gallrat) finns Knärot. Inget område hade någon Hänsynsmarkering för Knärot. Uppskattat antal. En miljöbild tagen i samma anmälan (76, 77)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123712996</v>
+        <v>123749142</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>5176</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,53 +947,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sågen, Dlr</t>
+          <t>SÅGEN, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514809</v>
+        <v>514789</v>
       </c>
       <c r="R4" t="n">
-        <v>6731156</v>
+        <v>6731161</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1022,7 +1015,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,12 +1025,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Två bilder på en av körvägarna i den ännu bara avverkningsanmälda skogen. Bilderna visar båda riktningar. Med vit sten, 74° ÖNÖ, N 514796, Ö 9731169 (10)  Lerig väg, 269° W, N 514794 Ö 6731162 (11)</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,7 +1058,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123713000</v>
+        <v>123712997</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1100,7 +1093,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1113,14 +1106,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sågen, Dlr</t>
+          <t>sågen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514819</v>
+        <v>514808</v>
       </c>
       <c r="R5" t="n">
-        <v>6731154</v>
+        <v>6731147</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1152,7 +1145,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1162,12 +1155,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>(05)</t>
+          <t>I angränsande avverkningsanmälan. I ravinen ner mot det troligen utdikade området. Uppskattat antal.  (08)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1188,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123749142</v>
+        <v>123713005</v>
       </c>
       <c r="B6" t="n">
-        <v>5176</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,46 +1200,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>SÅGEN, Dlr</t>
+          <t>sågen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514789</v>
+        <v>514848</v>
       </c>
       <c r="R6" t="n">
-        <v>6731161</v>
+        <v>6731141</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1285,12 +1285,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>En planta är uppdragen men det har inte jag gjord. Uppskattat antal, det kan vara flera.  (98)</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1318,7 +1318,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123713005</v>
+        <v>123713001</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514848</v>
+        <v>514842</v>
       </c>
       <c r="R7" t="n">
-        <v>6731141</v>
+        <v>6731143</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>En planta är uppdragen men det har inte jag gjord. Uppskattat antal, det kan vara flera.  (98)</t>
+          <t>(03)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1448,7 +1448,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123712998</v>
+        <v>123713000</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1496,14 +1496,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>sågen, Dlr</t>
+          <t>Sågen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514817</v>
+        <v>514819</v>
       </c>
       <c r="R8" t="n">
-        <v>6731152</v>
+        <v>6731154</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>(06) (07)</t>
+          <t>(05)</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1578,7 +1578,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123712972</v>
+        <v>123712996</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514858</v>
+        <v>514809</v>
       </c>
       <c r="R9" t="n">
-        <v>6731044</v>
+        <v>6731156</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>En bild på Knärot från en giltig avverkningsanmälan mellan en ännu ej giltig anmälan och en avverkad anmälan. I alla tre, samt i ett område som Mellanskog har gallrat) finns Knärot. Inget område hade någon Hänsynsmarkering för Knärot. Uppskattat antal. En miljöbild tagen i samma anmälan (76, 77)</t>
+          <t>Två bilder på en av körvägarna i den ännu bara avverkningsanmälda skogen. Bilderna visar båda riktningar. Med vit sten, 74° ÖNÖ, N 514796, Ö 9731169 (10)  Lerig väg, 269° W, N 514794 Ö 6731162 (11)</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 2055-2025 artfynd.xlsx
+++ b/artfynd/A 2055-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123712998</v>
+        <v>123749142</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>sågen, Dlr</t>
+          <t>SÅGEN, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514817</v>
+        <v>514789</v>
       </c>
       <c r="R2" t="n">
-        <v>6731152</v>
+        <v>6731161</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>(06) (07)</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -808,12 +796,7 @@
         <v>123712972</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,58 +918,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123749142</v>
+        <v>123712996</v>
       </c>
       <c r="B4" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SÅGEN, Dlr</t>
+          <t>Sågen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514789</v>
+        <v>514809</v>
       </c>
       <c r="R4" t="n">
-        <v>6731161</v>
+        <v>6731156</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1015,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1025,12 +1010,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>Två bilder på en av körvägarna i den ännu bara avverkningsanmälda skogen. Bilderna visar båda riktningar. Med vit sten, 74° ÖNÖ, N 514796, Ö 9731169 (10)  Lerig väg, 269° W, N 514794 Ö 6731162 (11)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1061,12 +1046,7 @@
         <v>123712997</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,15 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123713005</v>
+        <v>123712998</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1198,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1240,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514848</v>
+        <v>514817</v>
       </c>
       <c r="R6" t="n">
-        <v>6731141</v>
+        <v>6731152</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1275,7 +1250,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1285,12 +1260,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>En planta är uppdragen men det har inte jag gjord. Uppskattat antal, det kan vara flera.  (98)</t>
+          <t>(06) (07)</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1318,15 +1293,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123713001</v>
+        <v>123713000</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1323,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1366,14 +1336,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>sågen, Dlr</t>
+          <t>Sågen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514842</v>
+        <v>514819</v>
       </c>
       <c r="R7" t="n">
-        <v>6731143</v>
+        <v>6731154</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1405,7 +1375,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1415,12 +1385,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>(03)</t>
+          <t>(05)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1448,15 +1418,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123713000</v>
+        <v>123713001</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1448,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1496,14 +1461,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sågen, Dlr</t>
+          <t>sågen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514819</v>
+        <v>514842</v>
       </c>
       <c r="R8" t="n">
-        <v>6731154</v>
+        <v>6731143</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1535,7 +1500,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1545,12 +1510,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>(05)</t>
+          <t>(03)</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1578,15 +1543,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123712996</v>
+        <v>123713003</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1573,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1626,14 +1586,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sågen, Dlr</t>
+          <t>sågen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514809</v>
+        <v>514855</v>
       </c>
       <c r="R9" t="n">
-        <v>6731156</v>
+        <v>6731147</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1665,7 +1625,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1675,12 +1635,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Två bilder på en av körvägarna i den ännu bara avverkningsanmälda skogen. Bilderna visar båda riktningar. Med vit sten, 74° ÖNÖ, N 514796, Ö 9731169 (10)  Lerig väg, 269° W, N 514794 Ö 6731162 (11)</t>
+          <t>Uppskattat antal,  (00)</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1708,15 +1668,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123957572</v>
+        <v>123713004</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,17 +1696,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>sågen, Dlr</t>
+          <t>Sågen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514796</v>
+        <v>514849</v>
       </c>
       <c r="R10" t="n">
-        <v>6731092</v>
+        <v>6731149</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1778,22 +1741,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Uppskattat antal, kan vara fler. (97)</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1802,6 +1770,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1817,6 +1786,846 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123713005</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>sågen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>514848</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6731141</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>En planta är uppdragen men det har inte jag gjord. Uppskattat antal, det kan vara flera.  (98)</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123713006</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sågen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>514845</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6731155</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>(96)</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123713007</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>sågen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>514843</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6731144</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Att knäroten är så gul beror på att det går helt nyligen använd skogsmaskinväg där en tung skogsmaskin ca 20 meter från knärotslokalen.  (95)</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123713009</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>sågen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>514840</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6731150</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Variegata. Nära en väg som använts av tung skogsmaskin i sedan snön gick bort.  (94)</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123713010</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sågen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>514840</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6731149</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>(93)</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123957572</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>sågen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>514796</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6731092</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19:43</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:43</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123713002</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sågen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>514860</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6731147</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2055-2025 artfynd.xlsx
+++ b/artfynd/A 2055-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123749142</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123712972</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1040,6 +1055,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123712996</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1165,6 +1185,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123712997</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1290,6 +1315,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123712998</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1415,6 +1445,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123713000</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1540,6 +1575,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123713001</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1665,6 +1705,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123713003</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1786,6 +1831,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123713004</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1911,6 +1961,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123713005</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2036,6 +2091,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123713006</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2157,6 +2217,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123713007</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2282,6 +2347,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123713009</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2407,6 +2477,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123713010</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2514,6 +2589,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123957572</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2626,8 +2706,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123713002</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>